--- a/templates/기간제교원_발령대장(양식).xlsx
+++ b/templates/기간제교원_발령대장(양식).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\손승희\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E5CF5D-B723-4BC7-B281-EB0442D2744B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6998C6-6020-46A7-88F0-06F2C62CA39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13035" yWindow="645" windowWidth="16050" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,7 +375,7 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>예) 홍길동</t>
+    <t>홍길동</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1349,7 +1349,7 @@
       <c r="B2" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="31" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="38" t="s">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D5" s="8" t="str">
         <f>IF($A5="","",발령대장_입력!$C2)</f>
-        <v>예) 홍길동</v>
+        <v>홍길동</v>
       </c>
       <c r="E5" s="8" t="str">
         <f>IF($A5="","",발령대장_입력!$A2&amp;"에 임함"&amp;IF(발령대장_입력!$B2="","",CHAR(10)&amp;"("&amp;발령대장_입력!$B2&amp;")")&amp;IF(발령대장_입력!$G2="","",CHAR(10)&amp;"("&amp;SUBSTITUTE(SUBSTITUTE(발령대장_입력!$G2,"호봉","")," ","")&amp;")호봉을 급함")&amp;CHAR(10)&amp;"임용기간: "&amp;YEAR(발령대장_입력!$E2)&amp;"."&amp;MONTH(발령대장_입력!$E2)&amp;"."&amp;DAY(발령대장_입력!$E2)&amp;"."&amp;" ~ "&amp;YEAR(발령대장_입력!$F2)&amp;"."&amp;MONTH(발령대장_입력!$F2)&amp;"."&amp;DAY(발령대장_입력!$F2)&amp;".")</f>

--- a/templates/기간제교원_발령대장(양식).xlsx
+++ b/templates/기간제교원_발령대장(양식).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\손승희\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9120D9AE-C76F-4DF2-B5D2-8EC6EBC7D9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB37B600-3309-4F1D-8E76-B41AC0F65ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7395" yWindow="1200" windowWidth="18945" windowHeight="14025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기본설정·안내" sheetId="1" r:id="rId1"/>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="D6" s="8" t="str">
-        <f>IF($A6="","",발령대장_입력!$C3)</f>
+        <f ca="1">IF($A6="","",발령대장_입력!$C3&amp;IF(발령대장_입력!$D3="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D3),LEN(TEXT(발령대장_입력!$D3,"0"))&lt;6),TEXT(발령대장_입력!$D3,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D3),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D3),"yyyy. m. d."),발령대장_입력!$D3)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E6" s="8" t="str">
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
       <c r="D7" s="8" t="str">
-        <f>IF($A7="","",발령대장_입력!$C4)</f>
+        <f ca="1">IF($A7="","",발령대장_입력!$C4&amp;IF(발령대장_입력!$D4="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D4),LEN(TEXT(발령대장_입력!$D4,"0"))&lt;6),TEXT(발령대장_입력!$D4,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D4),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D4),"yyyy. m. d."),발령대장_입력!$D4)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E7" s="8" t="str">
@@ -3507,7 +3507,7 @@
         <v/>
       </c>
       <c r="D8" s="8" t="str">
-        <f>IF($A8="","",발령대장_입력!$C5)</f>
+        <f ca="1">IF($A8="","",발령대장_입력!$C5&amp;IF(발령대장_입력!$D5="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D5),LEN(TEXT(발령대장_입력!$D5,"0"))&lt;6),TEXT(발령대장_입력!$D5,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D5),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D5),"yyyy. m. d."),발령대장_입력!$D5)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E8" s="8" t="str">
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="D9" s="8" t="str">
-        <f>IF($A9="","",발령대장_입력!$C6)</f>
+        <f ca="1">IF($A9="","",발령대장_입력!$C6&amp;IF(발령대장_입력!$D6="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D6),LEN(TEXT(발령대장_입력!$D6,"0"))&lt;6),TEXT(발령대장_입력!$D6,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D6),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D6),"yyyy. m. d."),발령대장_입력!$D6)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E9" s="8" t="str">
@@ -3591,7 +3591,7 @@
         <v/>
       </c>
       <c r="D10" s="8" t="str">
-        <f>IF($A10="","",발령대장_입력!$C7)</f>
+        <f ca="1">IF($A10="","",발령대장_입력!$C7&amp;IF(발령대장_입력!$D7="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D7),LEN(TEXT(발령대장_입력!$D7,"0"))&lt;6),TEXT(발령대장_입력!$D7,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D7),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D7),"yyyy. m. d."),발령대장_입력!$D7)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E10" s="8" t="str">
@@ -3633,7 +3633,7 @@
         <v/>
       </c>
       <c r="D11" s="8" t="str">
-        <f>IF($A11="","",발령대장_입력!$C8)</f>
+        <f ca="1">IF($A11="","",발령대장_입력!$C8&amp;IF(발령대장_입력!$D8="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D8),LEN(TEXT(발령대장_입력!$D8,"0"))&lt;6),TEXT(발령대장_입력!$D8,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D8),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D8),"yyyy. m. d."),발령대장_입력!$D8)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E11" s="8" t="str">
@@ -3675,7 +3675,7 @@
         <v/>
       </c>
       <c r="D12" s="8" t="str">
-        <f>IF($A12="","",발령대장_입력!$C9)</f>
+        <f ca="1">IF($A12="","",발령대장_입력!$C9&amp;IF(발령대장_입력!$D9="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D9),LEN(TEXT(발령대장_입력!$D9,"0"))&lt;6),TEXT(발령대장_입력!$D9,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D9),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D9),"yyyy. m. d."),발령대장_입력!$D9)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E12" s="8" t="str">
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="D13" s="8" t="str">
-        <f>IF($A13="","",발령대장_입력!$C10)</f>
+        <f ca="1">IF($A13="","",발령대장_입력!$C10&amp;IF(발령대장_입력!$D10="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D10),LEN(TEXT(발령대장_입력!$D10,"0"))&lt;6),TEXT(발령대장_입력!$D10,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D10),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D10),"yyyy. m. d."),발령대장_입력!$D10)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E13" s="8" t="str">
@@ -3759,7 +3759,7 @@
         <v/>
       </c>
       <c r="D14" s="8" t="str">
-        <f>IF($A14="","",발령대장_입력!$C11)</f>
+        <f ca="1">IF($A14="","",발령대장_입력!$C11&amp;IF(발령대장_입력!$D11="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D11),LEN(TEXT(발령대장_입력!$D11,"0"))&lt;6),TEXT(발령대장_입력!$D11,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D11),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D11),"yyyy. m. d."),발령대장_입력!$D11)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E14" s="8" t="str">
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="D15" s="8" t="str">
-        <f>IF($A15="","",발령대장_입력!$C12)</f>
+        <f ca="1">IF($A15="","",발령대장_입력!$C12&amp;IF(발령대장_입력!$D12="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D12),LEN(TEXT(발령대장_입력!$D12,"0"))&lt;6),TEXT(발령대장_입력!$D12,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D12),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D12),"yyyy. m. d."),발령대장_입력!$D12)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E15" s="8" t="str">
@@ -3843,7 +3843,7 @@
         <v/>
       </c>
       <c r="D16" s="8" t="str">
-        <f>IF($A16="","",발령대장_입력!$C13)</f>
+        <f ca="1">IF($A16="","",발령대장_입력!$C13&amp;IF(발령대장_입력!$D13="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D13),LEN(TEXT(발령대장_입력!$D13,"0"))&lt;6),TEXT(발령대장_입력!$D13,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D13),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D13),"yyyy. m. d."),발령대장_입력!$D13)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E16" s="8" t="str">
@@ -3885,7 +3885,7 @@
         <v/>
       </c>
       <c r="D17" s="8" t="str">
-        <f>IF($A17="","",발령대장_입력!$C14)</f>
+        <f ca="1">IF($A17="","",발령대장_입력!$C14&amp;IF(발령대장_입력!$D14="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D14),LEN(TEXT(발령대장_입력!$D14,"0"))&lt;6),TEXT(발령대장_입력!$D14,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D14),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D14),"yyyy. m. d."),발령대장_입력!$D14)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E17" s="8" t="str">
@@ -3927,7 +3927,7 @@
         <v/>
       </c>
       <c r="D18" s="8" t="str">
-        <f>IF($A18="","",발령대장_입력!$C15)</f>
+        <f ca="1">IF($A18="","",발령대장_입력!$C15&amp;IF(발령대장_입력!$D15="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D15),LEN(TEXT(발령대장_입력!$D15,"0"))&lt;6),TEXT(발령대장_입력!$D15,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D15),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D15),"yyyy. m. d."),발령대장_입력!$D15)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E18" s="8" t="str">
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="D19" s="8" t="str">
-        <f>IF($A19="","",발령대장_입력!$C16)</f>
+        <f ca="1">IF($A19="","",발령대장_입력!$C16&amp;IF(발령대장_입력!$D16="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D16),LEN(TEXT(발령대장_입력!$D16,"0"))&lt;6),TEXT(발령대장_입력!$D16,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D16),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D16),"yyyy. m. d."),발령대장_입력!$D16)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E19" s="8" t="str">
@@ -4011,7 +4011,7 @@
         <v/>
       </c>
       <c r="D20" s="8" t="str">
-        <f>IF($A20="","",발령대장_입력!$C17)</f>
+        <f ca="1">IF($A20="","",발령대장_입력!$C17&amp;IF(발령대장_입력!$D17="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D17),LEN(TEXT(발령대장_입력!$D17,"0"))&lt;6),TEXT(발령대장_입력!$D17,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D17),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D17),"yyyy. m. d."),발령대장_입력!$D17)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E20" s="8" t="str">
@@ -4053,7 +4053,7 @@
         <v/>
       </c>
       <c r="D21" s="8" t="str">
-        <f>IF($A21="","",발령대장_입력!$C18)</f>
+        <f ca="1">IF($A21="","",발령대장_입력!$C18&amp;IF(발령대장_입력!$D18="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D18),LEN(TEXT(발령대장_입력!$D18,"0"))&lt;6),TEXT(발령대장_입력!$D18,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D18),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D18),"yyyy. m. d."),발령대장_입력!$D18)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E21" s="8" t="str">
@@ -4095,7 +4095,7 @@
         <v/>
       </c>
       <c r="D22" s="8" t="str">
-        <f>IF($A22="","",발령대장_입력!$C19)</f>
+        <f ca="1">IF($A22="","",발령대장_입력!$C19&amp;IF(발령대장_입력!$D19="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D19),LEN(TEXT(발령대장_입력!$D19,"0"))&lt;6),TEXT(발령대장_입력!$D19,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D19),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D19),"yyyy. m. d."),발령대장_입력!$D19)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E22" s="8" t="str">
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="D23" s="8" t="str">
-        <f>IF($A23="","",발령대장_입력!$C20)</f>
+        <f ca="1">IF($A23="","",발령대장_입력!$C20&amp;IF(발령대장_입력!$D20="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D20),LEN(TEXT(발령대장_입력!$D20,"0"))&lt;6),TEXT(발령대장_입력!$D20,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D20),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D20),"yyyy. m. d."),발령대장_입력!$D20)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E23" s="8" t="str">
@@ -4179,7 +4179,7 @@
         <v/>
       </c>
       <c r="D24" s="8" t="str">
-        <f>IF($A24="","",발령대장_입력!$C21)</f>
+        <f ca="1">IF($A24="","",발령대장_입력!$C21&amp;IF(발령대장_입력!$D21="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D21),LEN(TEXT(발령대장_입력!$D21,"0"))&lt;6),TEXT(발령대장_입력!$D21,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D21),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D21),"yyyy. m. d."),발령대장_입력!$D21)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E24" s="8" t="str">
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="D25" s="8" t="str">
-        <f>IF($A25="","",발령대장_입력!$C22)</f>
+        <f ca="1">IF($A25="","",발령대장_입력!$C22&amp;IF(발령대장_입력!$D22="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D22),LEN(TEXT(발령대장_입력!$D22,"0"))&lt;6),TEXT(발령대장_입력!$D22,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D22),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D22),"yyyy. m. d."),발령대장_입력!$D22)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E25" s="8" t="str">
@@ -4263,7 +4263,7 @@
         <v/>
       </c>
       <c r="D26" s="8" t="str">
-        <f>IF($A26="","",발령대장_입력!$C23)</f>
+        <f ca="1">IF($A26="","",발령대장_입력!$C23&amp;IF(발령대장_입력!$D23="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D23),LEN(TEXT(발령대장_입력!$D23,"0"))&lt;6),TEXT(발령대장_입력!$D23,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D23),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D23),"yyyy. m. d."),발령대장_입력!$D23)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E26" s="8" t="str">
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="D27" s="8" t="str">
-        <f>IF($A27="","",발령대장_입력!$C24)</f>
+        <f ca="1">IF($A27="","",발령대장_입력!$C24&amp;IF(발령대장_입력!$D24="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D24),LEN(TEXT(발령대장_입력!$D24,"0"))&lt;6),TEXT(발령대장_입력!$D24,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D24),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D24),"yyyy. m. d."),발령대장_입력!$D24)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E27" s="8" t="str">
@@ -4347,7 +4347,7 @@
         <v/>
       </c>
       <c r="D28" s="8" t="str">
-        <f>IF($A28="","",발령대장_입력!$C25)</f>
+        <f ca="1">IF($A28="","",발령대장_입력!$C25&amp;IF(발령대장_입력!$D25="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D25),LEN(TEXT(발령대장_입력!$D25,"0"))&lt;6),TEXT(발령대장_입력!$D25,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D25),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D25),"yyyy. m. d."),발령대장_입력!$D25)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E28" s="8" t="str">
@@ -4389,7 +4389,7 @@
         <v/>
       </c>
       <c r="D29" s="8" t="str">
-        <f>IF($A29="","",발령대장_입력!$C26)</f>
+        <f ca="1">IF($A29="","",발령대장_입력!$C26&amp;IF(발령대장_입력!$D26="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D26),LEN(TEXT(발령대장_입력!$D26,"0"))&lt;6),TEXT(발령대장_입력!$D26,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D26),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D26),"yyyy. m. d."),발령대장_입력!$D26)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E29" s="8" t="str">
@@ -4431,7 +4431,7 @@
         <v/>
       </c>
       <c r="D30" s="8" t="str">
-        <f>IF($A30="","",발령대장_입력!$C27)</f>
+        <f ca="1">IF($A30="","",발령대장_입력!$C27&amp;IF(발령대장_입력!$D27="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D27),LEN(TEXT(발령대장_입력!$D27,"0"))&lt;6),TEXT(발령대장_입력!$D27,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D27),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D27),"yyyy. m. d."),발령대장_입력!$D27)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E30" s="8" t="str">
@@ -4473,7 +4473,7 @@
         <v/>
       </c>
       <c r="D31" s="8" t="str">
-        <f>IF($A31="","",발령대장_입력!$C28)</f>
+        <f ca="1">IF($A31="","",발령대장_입력!$C28&amp;IF(발령대장_입력!$D28="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D28),LEN(TEXT(발령대장_입력!$D28,"0"))&lt;6),TEXT(발령대장_입력!$D28,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D28),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D28),"yyyy. m. d."),발령대장_입력!$D28)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E31" s="8" t="str">
@@ -4515,7 +4515,7 @@
         <v/>
       </c>
       <c r="D32" s="8" t="str">
-        <f>IF($A32="","",발령대장_입력!$C29)</f>
+        <f ca="1">IF($A32="","",발령대장_입력!$C29&amp;IF(발령대장_입력!$D29="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D29),LEN(TEXT(발령대장_입력!$D29,"0"))&lt;6),TEXT(발령대장_입력!$D29,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D29),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D29),"yyyy. m. d."),발령대장_입력!$D29)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E32" s="8" t="str">
@@ -4557,7 +4557,7 @@
         <v/>
       </c>
       <c r="D33" s="8" t="str">
-        <f>IF($A33="","",발령대장_입력!$C30)</f>
+        <f ca="1">IF($A33="","",발령대장_입력!$C30&amp;IF(발령대장_입력!$D30="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D30),LEN(TEXT(발령대장_입력!$D30,"0"))&lt;6),TEXT(발령대장_입력!$D30,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D30),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D30),"yyyy. m. d."),발령대장_입력!$D30)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E33" s="8" t="str">
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="D34" s="8" t="str">
-        <f>IF($A34="","",발령대장_입력!$C31)</f>
+        <f ca="1">IF($A34="","",발령대장_입력!$C31&amp;IF(발령대장_입력!$D31="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D31),LEN(TEXT(발령대장_입력!$D31,"0"))&lt;6),TEXT(발령대장_입력!$D31,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D31),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D31),"yyyy. m. d."),발령대장_입력!$D31)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E34" s="8" t="str">
@@ -4641,7 +4641,7 @@
         <v/>
       </c>
       <c r="D35" s="8" t="str">
-        <f>IF($A35="","",발령대장_입력!$C32)</f>
+        <f ca="1">IF($A35="","",발령대장_입력!$C32&amp;IF(발령대장_입력!$D32="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D32),LEN(TEXT(발령대장_입력!$D32,"0"))&lt;6),TEXT(발령대장_입력!$D32,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D32),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D32),"yyyy. m. d."),발령대장_입력!$D32)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E35" s="8" t="str">
@@ -4683,7 +4683,7 @@
         <v/>
       </c>
       <c r="D36" s="8" t="str">
-        <f>IF($A36="","",발령대장_입력!$C33)</f>
+        <f ca="1">IF($A36="","",발령대장_입력!$C33&amp;IF(발령대장_입력!$D33="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D33),LEN(TEXT(발령대장_입력!$D33,"0"))&lt;6),TEXT(발령대장_입력!$D33,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D33),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D33),"yyyy. m. d."),발령대장_입력!$D33)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E36" s="8" t="str">
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D37" s="8" t="str">
-        <f>IF($A37="","",발령대장_입력!$C34)</f>
+        <f ca="1">IF($A37="","",발령대장_입력!$C34&amp;IF(발령대장_입력!$D34="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D34),LEN(TEXT(발령대장_입력!$D34,"0"))&lt;6),TEXT(발령대장_입력!$D34,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D34),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D34),"yyyy. m. d."),발령대장_입력!$D34)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E37" s="8" t="str">
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="D38" s="8" t="str">
-        <f>IF($A38="","",발령대장_입력!$C35)</f>
+        <f ca="1">IF($A38="","",발령대장_입력!$C35&amp;IF(발령대장_입력!$D35="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D35),LEN(TEXT(발령대장_입력!$D35,"0"))&lt;6),TEXT(발령대장_입력!$D35,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D35),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D35),"yyyy. m. d."),발령대장_입력!$D35)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E38" s="8" t="str">
@@ -4809,7 +4809,7 @@
         <v/>
       </c>
       <c r="D39" s="8" t="str">
-        <f>IF($A39="","",발령대장_입력!$C36)</f>
+        <f ca="1">IF($A39="","",발령대장_입력!$C36&amp;IF(발령대장_입력!$D36="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D36),LEN(TEXT(발령대장_입력!$D36,"0"))&lt;6),TEXT(발령대장_입력!$D36,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D36),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D36),"yyyy. m. d."),발령대장_입력!$D36)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E39" s="8" t="str">
@@ -4851,7 +4851,7 @@
         <v/>
       </c>
       <c r="D40" s="8" t="str">
-        <f>IF($A40="","",발령대장_입력!$C37)</f>
+        <f ca="1">IF($A40="","",발령대장_입력!$C37&amp;IF(발령대장_입력!$D37="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D37),LEN(TEXT(발령대장_입력!$D37,"0"))&lt;6),TEXT(발령대장_입력!$D37,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D37),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D37),"yyyy. m. d."),발령대장_입력!$D37)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E40" s="8" t="str">
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="D41" s="8" t="str">
-        <f>IF($A41="","",발령대장_입력!$C38)</f>
+        <f ca="1">IF($A41="","",발령대장_입력!$C38&amp;IF(발령대장_입력!$D38="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D38),LEN(TEXT(발령대장_입력!$D38,"0"))&lt;6),TEXT(발령대장_입력!$D38,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D38),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D38),"yyyy. m. d."),발령대장_입력!$D38)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E41" s="8" t="str">
@@ -4935,7 +4935,7 @@
         <v/>
       </c>
       <c r="D42" s="8" t="str">
-        <f>IF($A42="","",발령대장_입력!$C39)</f>
+        <f ca="1">IF($A42="","",발령대장_입력!$C39&amp;IF(발령대장_입력!$D39="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D39),LEN(TEXT(발령대장_입력!$D39,"0"))&lt;6),TEXT(발령대장_입력!$D39,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D39),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D39),"yyyy. m. d."),발령대장_입력!$D39)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E42" s="8" t="str">
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="D43" s="8" t="str">
-        <f>IF($A43="","",발령대장_입력!$C40)</f>
+        <f ca="1">IF($A43="","",발령대장_입력!$C40&amp;IF(발령대장_입력!$D40="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D40),LEN(TEXT(발령대장_입력!$D40,"0"))&lt;6),TEXT(발령대장_입력!$D40,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D40),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D40),"yyyy. m. d."),발령대장_입력!$D40)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E43" s="8" t="str">
@@ -5019,7 +5019,7 @@
         <v/>
       </c>
       <c r="D44" s="8" t="str">
-        <f>IF($A44="","",발령대장_입력!$C41)</f>
+        <f ca="1">IF($A44="","",발령대장_입력!$C41&amp;IF(발령대장_입력!$D41="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D41),LEN(TEXT(발령대장_입력!$D41,"0"))&lt;6),TEXT(발령대장_입력!$D41,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D41),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D41),"yyyy. m. d."),발령대장_입력!$D41)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E44" s="8" t="str">
@@ -5061,7 +5061,7 @@
         <v/>
       </c>
       <c r="D45" s="8" t="str">
-        <f>IF($A45="","",발령대장_입력!$C42)</f>
+        <f ca="1">IF($A45="","",발령대장_입력!$C42&amp;IF(발령대장_입력!$D42="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D42),LEN(TEXT(발령대장_입력!$D42,"0"))&lt;6),TEXT(발령대장_입력!$D42,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D42),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D42),"yyyy. m. d."),발령대장_입력!$D42)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E45" s="8" t="str">
@@ -5103,7 +5103,7 @@
         <v/>
       </c>
       <c r="D46" s="8" t="str">
-        <f>IF($A46="","",발령대장_입력!$C43)</f>
+        <f ca="1">IF($A46="","",발령대장_입력!$C43&amp;IF(발령대장_입력!$D43="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D43),LEN(TEXT(발령대장_입력!$D43,"0"))&lt;6),TEXT(발령대장_입력!$D43,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D43),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D43),"yyyy. m. d."),발령대장_입력!$D43)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E46" s="8" t="str">
@@ -5145,7 +5145,7 @@
         <v/>
       </c>
       <c r="D47" s="8" t="str">
-        <f>IF($A47="","",발령대장_입력!$C44)</f>
+        <f ca="1">IF($A47="","",발령대장_입력!$C44&amp;IF(발령대장_입력!$D44="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D44),LEN(TEXT(발령대장_입력!$D44,"0"))&lt;6),TEXT(발령대장_입력!$D44,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D44),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D44),"yyyy. m. d."),발령대장_입력!$D44)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E47" s="8" t="str">
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="D48" s="8" t="str">
-        <f>IF($A48="","",발령대장_입력!$C45)</f>
+        <f ca="1">IF($A48="","",발령대장_입력!$C45&amp;IF(발령대장_입력!$D45="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D45),LEN(TEXT(발령대장_입력!$D45,"0"))&lt;6),TEXT(발령대장_입력!$D45,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D45),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D45),"yyyy. m. d."),발령대장_입력!$D45)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E48" s="8" t="str">
@@ -5229,7 +5229,7 @@
         <v/>
       </c>
       <c r="D49" s="8" t="str">
-        <f>IF($A49="","",발령대장_입력!$C46)</f>
+        <f ca="1">IF($A49="","",발령대장_입력!$C46&amp;IF(발령대장_입력!$D46="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D46),LEN(TEXT(발령대장_입력!$D46,"0"))&lt;6),TEXT(발령대장_입력!$D46,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D46),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D46),"yyyy. m. d."),발령대장_입력!$D46)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E49" s="8" t="str">
@@ -5271,7 +5271,7 @@
         <v/>
       </c>
       <c r="D50" s="8" t="str">
-        <f>IF($A50="","",발령대장_입력!$C47)</f>
+        <f ca="1">IF($A50="","",발령대장_입력!$C47&amp;IF(발령대장_입력!$D47="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D47),LEN(TEXT(발령대장_입력!$D47,"0"))&lt;6),TEXT(발령대장_입력!$D47,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D47),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D47),"yyyy. m. d."),발령대장_입력!$D47)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E50" s="8" t="str">
@@ -5313,7 +5313,7 @@
         <v/>
       </c>
       <c r="D51" s="8" t="str">
-        <f>IF($A51="","",발령대장_입력!$C48)</f>
+        <f ca="1">IF($A51="","",발령대장_입력!$C48&amp;IF(발령대장_입력!$D48="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D48),LEN(TEXT(발령대장_입력!$D48,"0"))&lt;6),TEXT(발령대장_입력!$D48,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D48),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D48),"yyyy. m. d."),발령대장_입력!$D48)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E51" s="8" t="str">
@@ -5355,7 +5355,7 @@
         <v/>
       </c>
       <c r="D52" s="8" t="str">
-        <f>IF($A52="","",발령대장_입력!$C49)</f>
+        <f ca="1">IF($A52="","",발령대장_입력!$C49&amp;IF(발령대장_입력!$D49="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D49),LEN(TEXT(발령대장_입력!$D49,"0"))&lt;6),TEXT(발령대장_입력!$D49,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D49),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D49),"yyyy. m. d."),발령대장_입력!$D49)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E52" s="8" t="str">
@@ -5397,7 +5397,7 @@
         <v/>
       </c>
       <c r="D53" s="8" t="str">
-        <f>IF($A53="","",발령대장_입력!$C50)</f>
+        <f ca="1">IF($A53="","",발령대장_입력!$C50&amp;IF(발령대장_입력!$D50="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D50),LEN(TEXT(발령대장_입력!$D50,"0"))&lt;6),TEXT(발령대장_입력!$D50,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D50),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D50),"yyyy. m. d."),발령대장_입력!$D50)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E53" s="8" t="str">
@@ -5439,7 +5439,7 @@
         <v/>
       </c>
       <c r="D54" s="8" t="str">
-        <f>IF($A54="","",발령대장_입력!$C51)</f>
+        <f ca="1">IF($A54="","",발령대장_입력!$C51&amp;IF(발령대장_입력!$D51="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D51),LEN(TEXT(발령대장_입력!$D51,"0"))&lt;6),TEXT(발령대장_입력!$D51,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D51),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D51),"yyyy. m. d."),발령대장_입력!$D51)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E54" s="8" t="str">
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="D55" s="8" t="str">
-        <f>IF($A55="","",발령대장_입력!$C52)</f>
+        <f ca="1">IF($A55="","",발령대장_입력!$C52&amp;IF(발령대장_입력!$D52="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D52),LEN(TEXT(발령대장_입력!$D52,"0"))&lt;6),TEXT(발령대장_입력!$D52,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D52),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D52),"yyyy. m. d."),발령대장_입력!$D52)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E55" s="8" t="str">
@@ -5523,7 +5523,7 @@
         <v/>
       </c>
       <c r="D56" s="8" t="str">
-        <f>IF($A56="","",발령대장_입력!$C53)</f>
+        <f ca="1">IF($A56="","",발령대장_입력!$C53&amp;IF(발령대장_입력!$D53="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D53),LEN(TEXT(발령대장_입력!$D53,"0"))&lt;6),TEXT(발령대장_입력!$D53,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D53),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D53),"yyyy. m. d."),발령대장_입력!$D53)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E56" s="8" t="str">
@@ -5565,7 +5565,7 @@
         <v/>
       </c>
       <c r="D57" s="8" t="str">
-        <f>IF($A57="","",발령대장_입력!$C54)</f>
+        <f ca="1">IF($A57="","",발령대장_입력!$C54&amp;IF(발령대장_입력!$D54="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D54),LEN(TEXT(발령대장_입력!$D54,"0"))&lt;6),TEXT(발령대장_입력!$D54,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D54),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D54),"yyyy. m. d."),발령대장_입력!$D54)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E57" s="8" t="str">
@@ -5607,7 +5607,7 @@
         <v/>
       </c>
       <c r="D58" s="8" t="str">
-        <f>IF($A58="","",발령대장_입력!$C55)</f>
+        <f ca="1">IF($A58="","",발령대장_입력!$C55&amp;IF(발령대장_입력!$D55="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D55),LEN(TEXT(발령대장_입력!$D55,"0"))&lt;6),TEXT(발령대장_입력!$D55,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D55),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D55),"yyyy. m. d."),발령대장_입력!$D55)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E58" s="8" t="str">
@@ -5649,7 +5649,7 @@
         <v/>
       </c>
       <c r="D59" s="8" t="str">
-        <f>IF($A59="","",발령대장_입력!$C56)</f>
+        <f ca="1">IF($A59="","",발령대장_입력!$C56&amp;IF(발령대장_입력!$D56="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D56),LEN(TEXT(발령대장_입력!$D56,"0"))&lt;6),TEXT(발령대장_입력!$D56,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D56),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D56),"yyyy. m. d."),발령대장_입력!$D56)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E59" s="8" t="str">
@@ -5691,7 +5691,7 @@
         <v/>
       </c>
       <c r="D60" s="8" t="str">
-        <f>IF($A60="","",발령대장_입력!$C57)</f>
+        <f ca="1">IF($A60="","",발령대장_입력!$C57&amp;IF(발령대장_입력!$D57="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D57),LEN(TEXT(발령대장_입력!$D57,"0"))&lt;6),TEXT(발령대장_입력!$D57,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D57),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D57),"yyyy. m. d."),발령대장_입력!$D57)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E60" s="8" t="str">
@@ -5733,7 +5733,7 @@
         <v/>
       </c>
       <c r="D61" s="8" t="str">
-        <f>IF($A61="","",발령대장_입력!$C58)</f>
+        <f ca="1">IF($A61="","",발령대장_입력!$C58&amp;IF(발령대장_입력!$D58="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D58),LEN(TEXT(발령대장_입력!$D58,"0"))&lt;6),TEXT(발령대장_입력!$D58,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D58),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D58),"yyyy. m. d."),발령대장_입력!$D58)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E61" s="8" t="str">
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="D62" s="8" t="str">
-        <f>IF($A62="","",발령대장_입력!$C59)</f>
+        <f ca="1">IF($A62="","",발령대장_입력!$C59&amp;IF(발령대장_입력!$D59="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D59),LEN(TEXT(발령대장_입력!$D59,"0"))&lt;6),TEXT(발령대장_입력!$D59,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D59),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D59),"yyyy. m. d."),발령대장_입력!$D59)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E62" s="8" t="str">
@@ -5817,7 +5817,7 @@
         <v/>
       </c>
       <c r="D63" s="8" t="str">
-        <f>IF($A63="","",발령대장_입력!$C60)</f>
+        <f ca="1">IF($A63="","",발령대장_입력!$C60&amp;IF(발령대장_입력!$D60="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D60),LEN(TEXT(발령대장_입력!$D60,"0"))&lt;6),TEXT(발령대장_입력!$D60,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D60),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D60),"yyyy. m. d."),발령대장_입력!$D60)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E63" s="8" t="str">
@@ -5859,7 +5859,7 @@
         <v/>
       </c>
       <c r="D64" s="8" t="str">
-        <f>IF($A64="","",발령대장_입력!$C61)</f>
+        <f ca="1">IF($A64="","",발령대장_입력!$C61&amp;IF(발령대장_입력!$D61="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D61),LEN(TEXT(발령대장_입력!$D61,"0"))&lt;6),TEXT(발령대장_입력!$D61,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D61),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D61),"yyyy. m. d."),발령대장_입력!$D61)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E64" s="8" t="str">
@@ -5901,7 +5901,7 @@
         <v/>
       </c>
       <c r="D65" s="8" t="str">
-        <f>IF($A65="","",발령대장_입력!$C62)</f>
+        <f ca="1">IF($A65="","",발령대장_입력!$C62&amp;IF(발령대장_입력!$D62="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D62),LEN(TEXT(발령대장_입력!$D62,"0"))&lt;6),TEXT(발령대장_입력!$D62,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D62),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D62),"yyyy. m. d."),발령대장_입력!$D62)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E65" s="8" t="str">
@@ -5943,7 +5943,7 @@
         <v/>
       </c>
       <c r="D66" s="8" t="str">
-        <f>IF($A66="","",발령대장_입력!$C63)</f>
+        <f ca="1">IF($A66="","",발령대장_입력!$C63&amp;IF(발령대장_입력!$D63="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D63),LEN(TEXT(발령대장_입력!$D63,"0"))&lt;6),TEXT(발령대장_입력!$D63,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D63),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D63),"yyyy. m. d."),발령대장_입력!$D63)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E66" s="8" t="str">
@@ -5985,7 +5985,7 @@
         <v/>
       </c>
       <c r="D67" s="8" t="str">
-        <f>IF($A67="","",발령대장_입력!$C64)</f>
+        <f ca="1">IF($A67="","",발령대장_입력!$C64&amp;IF(발령대장_입력!$D64="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D64),LEN(TEXT(발령대장_입력!$D64,"0"))&lt;6),TEXT(발령대장_입력!$D64,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D64),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D64),"yyyy. m. d."),발령대장_입력!$D64)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E67" s="8" t="str">
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="D68" s="8" t="str">
-        <f>IF($A68="","",발령대장_입력!$C65)</f>
+        <f ca="1">IF($A68="","",발령대장_입력!$C65&amp;IF(발령대장_입력!$D65="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D65),LEN(TEXT(발령대장_입력!$D65,"0"))&lt;6),TEXT(발령대장_입력!$D65,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D65),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D65),"yyyy. m. d."),발령대장_입력!$D65)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E68" s="8" t="str">
@@ -6069,7 +6069,7 @@
         <v/>
       </c>
       <c r="D69" s="8" t="str">
-        <f>IF($A69="","",발령대장_입력!$C66)</f>
+        <f ca="1">IF($A69="","",발령대장_입력!$C66&amp;IF(발령대장_입력!$D66="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D66),LEN(TEXT(발령대장_입력!$D66,"0"))&lt;6),TEXT(발령대장_입력!$D66,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D66),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D66),"yyyy. m. d."),발령대장_입력!$D66)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E69" s="8" t="str">
@@ -6111,7 +6111,7 @@
         <v/>
       </c>
       <c r="D70" s="8" t="str">
-        <f>IF($A70="","",발령대장_입력!$C67)</f>
+        <f ca="1">IF($A70="","",발령대장_입력!$C67&amp;IF(발령대장_입력!$D67="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D67),LEN(TEXT(발령대장_입력!$D67,"0"))&lt;6),TEXT(발령대장_입력!$D67,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D67),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D67),"yyyy. m. d."),발령대장_입력!$D67)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E70" s="8" t="str">
@@ -6153,7 +6153,7 @@
         <v/>
       </c>
       <c r="D71" s="8" t="str">
-        <f>IF($A71="","",발령대장_입력!$C68)</f>
+        <f ca="1">IF($A71="","",발령대장_입력!$C68&amp;IF(발령대장_입력!$D68="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D68),LEN(TEXT(발령대장_입력!$D68,"0"))&lt;6),TEXT(발령대장_입력!$D68,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D68),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D68),"yyyy. m. d."),발령대장_입력!$D68)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E71" s="8" t="str">
@@ -6195,7 +6195,7 @@
         <v/>
       </c>
       <c r="D72" s="8" t="str">
-        <f>IF($A72="","",발령대장_입력!$C69)</f>
+        <f ca="1">IF($A72="","",발령대장_입력!$C69&amp;IF(발령대장_입력!$D69="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D69),LEN(TEXT(발령대장_입력!$D69,"0"))&lt;6),TEXT(발령대장_입력!$D69,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D69),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D69),"yyyy. m. d."),발령대장_입력!$D69)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E72" s="8" t="str">
@@ -6237,7 +6237,7 @@
         <v/>
       </c>
       <c r="D73" s="8" t="str">
-        <f>IF($A73="","",발령대장_입력!$C70)</f>
+        <f ca="1">IF($A73="","",발령대장_입력!$C70&amp;IF(발령대장_입력!$D70="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D70),LEN(TEXT(발령대장_입력!$D70,"0"))&lt;6),TEXT(발령대장_입력!$D70,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D70),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D70),"yyyy. m. d."),발령대장_입력!$D70)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E73" s="8" t="str">
@@ -6279,7 +6279,7 @@
         <v/>
       </c>
       <c r="D74" s="8" t="str">
-        <f>IF($A74="","",발령대장_입력!$C71)</f>
+        <f ca="1">IF($A74="","",발령대장_입력!$C71&amp;IF(발령대장_입력!$D71="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D71),LEN(TEXT(발령대장_입력!$D71,"0"))&lt;6),TEXT(발령대장_입력!$D71,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D71),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D71),"yyyy. m. d."),발령대장_입력!$D71)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E74" s="8" t="str">
@@ -6321,7 +6321,7 @@
         <v/>
       </c>
       <c r="D75" s="8" t="str">
-        <f>IF($A75="","",발령대장_입력!$C72)</f>
+        <f ca="1">IF($A75="","",발령대장_입력!$C72&amp;IF(발령대장_입력!$D72="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D72),LEN(TEXT(발령대장_입력!$D72,"0"))&lt;6),TEXT(발령대장_입력!$D72,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D72),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D72),"yyyy. m. d."),발령대장_입력!$D72)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E75" s="8" t="str">
@@ -6363,7 +6363,7 @@
         <v/>
       </c>
       <c r="D76" s="8" t="str">
-        <f>IF($A76="","",발령대장_입력!$C73)</f>
+        <f ca="1">IF($A76="","",발령대장_입력!$C73&amp;IF(발령대장_입력!$D73="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D73),LEN(TEXT(발령대장_입력!$D73,"0"))&lt;6),TEXT(발령대장_입력!$D73,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D73),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D73),"yyyy. m. d."),발령대장_입력!$D73)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E76" s="8" t="str">
@@ -6405,7 +6405,7 @@
         <v/>
       </c>
       <c r="D77" s="8" t="str">
-        <f>IF($A77="","",발령대장_입력!$C74)</f>
+        <f ca="1">IF($A77="","",발령대장_입력!$C74&amp;IF(발령대장_입력!$D74="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D74),LEN(TEXT(발령대장_입력!$D74,"0"))&lt;6),TEXT(발령대장_입력!$D74,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D74),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D74),"yyyy. m. d."),발령대장_입력!$D74)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E77" s="8" t="str">
@@ -6447,7 +6447,7 @@
         <v/>
       </c>
       <c r="D78" s="8" t="str">
-        <f>IF($A78="","",발령대장_입력!$C75)</f>
+        <f ca="1">IF($A78="","",발령대장_입력!$C75&amp;IF(발령대장_입력!$D75="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D75),LEN(TEXT(발령대장_입력!$D75,"0"))&lt;6),TEXT(발령대장_입력!$D75,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D75),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D75),"yyyy. m. d."),발령대장_입력!$D75)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E78" s="8" t="str">
@@ -6489,7 +6489,7 @@
         <v/>
       </c>
       <c r="D79" s="8" t="str">
-        <f>IF($A79="","",발령대장_입력!$C76)</f>
+        <f ca="1">IF($A79="","",발령대장_입력!$C76&amp;IF(발령대장_입력!$D76="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D76),LEN(TEXT(발령대장_입력!$D76,"0"))&lt;6),TEXT(발령대장_입력!$D76,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D76),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D76),"yyyy. m. d."),발령대장_입력!$D76)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E79" s="8" t="str">
@@ -6531,7 +6531,7 @@
         <v/>
       </c>
       <c r="D80" s="8" t="str">
-        <f>IF($A80="","",발령대장_입력!$C77)</f>
+        <f ca="1">IF($A80="","",발령대장_입력!$C77&amp;IF(발령대장_입력!$D77="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D77),LEN(TEXT(발령대장_입력!$D77,"0"))&lt;6),TEXT(발령대장_입력!$D77,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D77),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D77),"yyyy. m. d."),발령대장_입력!$D77)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E80" s="8" t="str">
@@ -6573,7 +6573,7 @@
         <v/>
       </c>
       <c r="D81" s="8" t="str">
-        <f>IF($A81="","",발령대장_입력!$C78)</f>
+        <f ca="1">IF($A81="","",발령대장_입력!$C78&amp;IF(발령대장_입력!$D78="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D78),LEN(TEXT(발령대장_입력!$D78,"0"))&lt;6),TEXT(발령대장_입력!$D78,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D78),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D78),"yyyy. m. d."),발령대장_입력!$D78)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E81" s="8" t="str">
@@ -6615,7 +6615,7 @@
         <v/>
       </c>
       <c r="D82" s="8" t="str">
-        <f>IF($A82="","",발령대장_입력!$C79)</f>
+        <f ca="1">IF($A82="","",발령대장_입력!$C79&amp;IF(발령대장_입력!$D79="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D79),LEN(TEXT(발령대장_입력!$D79,"0"))&lt;6),TEXT(발령대장_입력!$D79,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D79),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D79),"yyyy. m. d."),발령대장_입력!$D79)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E82" s="8" t="str">
@@ -6657,7 +6657,7 @@
         <v/>
       </c>
       <c r="D83" s="8" t="str">
-        <f>IF($A83="","",발령대장_입력!$C80)</f>
+        <f ca="1">IF($A83="","",발령대장_입력!$C80&amp;IF(발령대장_입력!$D80="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D80),LEN(TEXT(발령대장_입력!$D80,"0"))&lt;6),TEXT(발령대장_입력!$D80,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D80),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D80),"yyyy. m. d."),발령대장_입력!$D80)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E83" s="8" t="str">
@@ -6699,7 +6699,7 @@
         <v/>
       </c>
       <c r="D84" s="8" t="str">
-        <f>IF($A84="","",발령대장_입력!$C81)</f>
+        <f ca="1">IF($A84="","",발령대장_입력!$C81&amp;IF(발령대장_입력!$D81="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D81),LEN(TEXT(발령대장_입력!$D81,"0"))&lt;6),TEXT(발령대장_입력!$D81,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D81),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D81),"yyyy. m. d."),발령대장_입력!$D81)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E84" s="8" t="str">
@@ -6741,7 +6741,7 @@
         <v/>
       </c>
       <c r="D85" s="8" t="str">
-        <f>IF($A85="","",발령대장_입력!$C82)</f>
+        <f ca="1">IF($A85="","",발령대장_입력!$C82&amp;IF(발령대장_입력!$D82="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D82),LEN(TEXT(발령대장_입력!$D82,"0"))&lt;6),TEXT(발령대장_입력!$D82,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D82),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D82),"yyyy. m. d."),발령대장_입력!$D82)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E85" s="8" t="str">
@@ -6783,7 +6783,7 @@
         <v/>
       </c>
       <c r="D86" s="8" t="str">
-        <f>IF($A86="","",발령대장_입력!$C83)</f>
+        <f ca="1">IF($A86="","",발령대장_입력!$C83&amp;IF(발령대장_입력!$D83="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D83),LEN(TEXT(발령대장_입력!$D83,"0"))&lt;6),TEXT(발령대장_입력!$D83,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D83),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D83),"yyyy. m. d."),발령대장_입력!$D83)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E86" s="8" t="str">
@@ -6825,7 +6825,7 @@
         <v/>
       </c>
       <c r="D87" s="8" t="str">
-        <f>IF($A87="","",발령대장_입력!$C84)</f>
+        <f ca="1">IF($A87="","",발령대장_입력!$C84&amp;IF(발령대장_입력!$D84="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D84),LEN(TEXT(발령대장_입력!$D84,"0"))&lt;6),TEXT(발령대장_입력!$D84,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D84),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D84),"yyyy. m. d."),발령대장_입력!$D84)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E87" s="8" t="str">
@@ -6867,7 +6867,7 @@
         <v/>
       </c>
       <c r="D88" s="8" t="str">
-        <f>IF($A88="","",발령대장_입력!$C85)</f>
+        <f ca="1">IF($A88="","",발령대장_입력!$C85&amp;IF(발령대장_입력!$D85="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D85),LEN(TEXT(발령대장_입력!$D85,"0"))&lt;6),TEXT(발령대장_입력!$D85,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D85),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D85),"yyyy. m. d."),발령대장_입력!$D85)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E88" s="8" t="str">
@@ -6909,7 +6909,7 @@
         <v/>
       </c>
       <c r="D89" s="8" t="str">
-        <f>IF($A89="","",발령대장_입력!$C86)</f>
+        <f ca="1">IF($A89="","",발령대장_입력!$C86&amp;IF(발령대장_입력!$D86="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D86),LEN(TEXT(발령대장_입력!$D86,"0"))&lt;6),TEXT(발령대장_입력!$D86,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D86),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D86),"yyyy. m. d."),발령대장_입력!$D86)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E89" s="8" t="str">
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D90" s="8" t="str">
-        <f>IF($A90="","",발령대장_입력!$C87)</f>
+        <f ca="1">IF($A90="","",발령대장_입력!$C87&amp;IF(발령대장_입력!$D87="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D87),LEN(TEXT(발령대장_입력!$D87,"0"))&lt;6),TEXT(발령대장_입력!$D87,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D87),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D87),"yyyy. m. d."),발령대장_입력!$D87)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E90" s="8" t="str">
@@ -6993,7 +6993,7 @@
         <v/>
       </c>
       <c r="D91" s="8" t="str">
-        <f>IF($A91="","",발령대장_입력!$C88)</f>
+        <f ca="1">IF($A91="","",발령대장_입력!$C88&amp;IF(발령대장_입력!$D88="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D88),LEN(TEXT(발령대장_입력!$D88,"0"))&lt;6),TEXT(발령대장_입력!$D88,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D88),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D88),"yyyy. m. d."),발령대장_입력!$D88)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E91" s="8" t="str">
@@ -7035,7 +7035,7 @@
         <v/>
       </c>
       <c r="D92" s="8" t="str">
-        <f>IF($A92="","",발령대장_입력!$C89)</f>
+        <f ca="1">IF($A92="","",발령대장_입력!$C89&amp;IF(발령대장_입력!$D89="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D89),LEN(TEXT(발령대장_입력!$D89,"0"))&lt;6),TEXT(발령대장_입력!$D89,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D89),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D89),"yyyy. m. d."),발령대장_입력!$D89)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E92" s="8" t="str">
@@ -7077,7 +7077,7 @@
         <v/>
       </c>
       <c r="D93" s="8" t="str">
-        <f>IF($A93="","",발령대장_입력!$C90)</f>
+        <f ca="1">IF($A93="","",발령대장_입력!$C90&amp;IF(발령대장_입력!$D90="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D90),LEN(TEXT(발령대장_입력!$D90,"0"))&lt;6),TEXT(발령대장_입력!$D90,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D90),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D90),"yyyy. m. d."),발령대장_입력!$D90)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E93" s="8" t="str">
@@ -7119,7 +7119,7 @@
         <v/>
       </c>
       <c r="D94" s="8" t="str">
-        <f>IF($A94="","",발령대장_입력!$C91)</f>
+        <f ca="1">IF($A94="","",발령대장_입력!$C91&amp;IF(발령대장_입력!$D91="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D91),LEN(TEXT(발령대장_입력!$D91,"0"))&lt;6),TEXT(발령대장_입력!$D91,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D91),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D91),"yyyy. m. d."),발령대장_입력!$D91)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E94" s="8" t="str">
@@ -7161,7 +7161,7 @@
         <v/>
       </c>
       <c r="D95" s="8" t="str">
-        <f>IF($A95="","",발령대장_입력!$C92)</f>
+        <f ca="1">IF($A95="","",발령대장_입력!$C92&amp;IF(발령대장_입력!$D92="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D92),LEN(TEXT(발령대장_입력!$D92,"0"))&lt;6),TEXT(발령대장_입력!$D92,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D92),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D92),"yyyy. m. d."),발령대장_입력!$D92)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E95" s="8" t="str">
@@ -7203,7 +7203,7 @@
         <v/>
       </c>
       <c r="D96" s="8" t="str">
-        <f>IF($A96="","",발령대장_입력!$C93)</f>
+        <f ca="1">IF($A96="","",발령대장_입력!$C93&amp;IF(발령대장_입력!$D93="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D93),LEN(TEXT(발령대장_입력!$D93,"0"))&lt;6),TEXT(발령대장_입력!$D93,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D93),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D93),"yyyy. m. d."),발령대장_입력!$D93)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E96" s="8" t="str">
@@ -7245,7 +7245,7 @@
         <v/>
       </c>
       <c r="D97" s="8" t="str">
-        <f>IF($A97="","",발령대장_입력!$C94)</f>
+        <f ca="1">IF($A97="","",발령대장_입력!$C94&amp;IF(발령대장_입력!$D94="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D94),LEN(TEXT(발령대장_입력!$D94,"0"))&lt;6),TEXT(발령대장_입력!$D94,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D94),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D94),"yyyy. m. d."),발령대장_입력!$D94)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E97" s="8" t="str">
@@ -7287,7 +7287,7 @@
         <v/>
       </c>
       <c r="D98" s="8" t="str">
-        <f>IF($A98="","",발령대장_입력!$C95)</f>
+        <f ca="1">IF($A98="","",발령대장_입력!$C95&amp;IF(발령대장_입력!$D95="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D95),LEN(TEXT(발령대장_입력!$D95,"0"))&lt;6),TEXT(발령대장_입력!$D95,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D95),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D95),"yyyy. m. d."),발령대장_입력!$D95)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E98" s="8" t="str">
@@ -7329,7 +7329,7 @@
         <v/>
       </c>
       <c r="D99" s="8" t="str">
-        <f>IF($A99="","",발령대장_입력!$C96)</f>
+        <f ca="1">IF($A99="","",발령대장_입력!$C96&amp;IF(발령대장_입력!$D96="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D96),LEN(TEXT(발령대장_입력!$D96,"0"))&lt;6),TEXT(발령대장_입력!$D96,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D96),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D96),"yyyy. m. d."),발령대장_입력!$D96)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E99" s="8" t="str">
@@ -7371,7 +7371,7 @@
         <v/>
       </c>
       <c r="D100" s="8" t="str">
-        <f>IF($A100="","",발령대장_입력!$C97)</f>
+        <f ca="1">IF($A100="","",발령대장_입력!$C97&amp;IF(발령대장_입력!$D97="","",CHAR(10)&amp;"("&amp;IF(AND(ISNUMBER(발령대장_입력!$D97),LEN(TEXT(발령대장_입력!$D97,"0"))&lt;6),TEXT(발령대장_입력!$D97,"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""))=13,TEXT(DATE(IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="1",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="2",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="5",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="6"),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2)),IF(OR(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="3",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="4",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="7",MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),7,1)="8"),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2)),1800+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2)))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),3,2)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),5,2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""))=8,TEXT(DATE(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),4)),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),5,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2))),"yyyy. m. d."),IF(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""))=6,TEXT(DATE(IF(VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2))&lt;=MOD(YEAR(TODAY()),100),2000+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2)),1900+VALUE(LEFT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2))),VALUE(MID(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),3,2)),VALUE(RIGHT(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TRIM(발령대장_입력!$D97),"-",""),".","")," ",""),2))),"yyyy. m. d."),IFERROR(TEXT(DATEVALUE(발령대장_입력!$D97),"yyyy. m. d."),발령대장_입력!$D97)))))&amp;")"))</f>
         <v/>
       </c>
       <c r="E100" s="8" t="str">

--- a/templates/기간제교원_발령대장(양식).xlsx
+++ b/templates/기간제교원_발령대장(양식).xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\손승희\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB37B600-3309-4F1D-8E76-B41AC0F65ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD69D0F1-BF15-448C-95DD-84DB50EC852E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기본설정·안내" sheetId="1" r:id="rId1"/>
     <sheet name="발령대장_입력" sheetId="2" r:id="rId2"/>
     <sheet name="발령대장_출력" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">발령대장_출력!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -3279,8 +3282,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11233,7 +11237,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>